--- a/RaidenDemo/文档/配置表/PlayerAircraftLevelResource.xlsx
+++ b/RaidenDemo/文档/配置表/PlayerAircraftLevelResource.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="105">
   <si>
     <t>##var</t>
   </si>
@@ -92,45 +92,39 @@
     <t>appearanceName</t>
   </si>
   <si>
+    <t>damagedAppearance</t>
+  </si>
+  <si>
+    <t>aircraftSizeType</t>
+  </si>
+  <si>
     <t>*collisionShapes</t>
   </si>
   <si>
-    <t>health</t>
-  </si>
-  <si>
-    <t>moveSpeed</t>
+    <t>*attributes</t>
   </si>
   <si>
     <t>*bulletLaunchers</t>
   </si>
   <si>
-    <t>*deathExplosions</t>
-  </si>
-  <si>
-    <t>removeAfterDeathPresentation</t>
-  </si>
-  <si>
     <t>外观资源名</t>
   </si>
   <si>
+    <t>战损外观资源名</t>
+  </si>
+  <si>
+    <t>飞行器体型</t>
+  </si>
+  <si>
     <t>碰撞形状列表</t>
   </si>
   <si>
-    <t>生命值</t>
-  </si>
-  <si>
-    <t>移动速度</t>
+    <t>基础属性列表</t>
   </si>
   <si>
     <t>子弹发射器列表</t>
   </si>
   <si>
-    <t>死亡前依次播放的爆炸效果列表</t>
-  </si>
-  <si>
-    <t>所有爆炸效果播放完成后是否移除自身</t>
-  </si>
-  <si>
     <t>$type</t>
   </si>
   <si>
@@ -143,6 +137,12 @@
     <t>pivot</t>
   </si>
   <si>
+    <t>attributeId</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
     <t>offset</t>
   </si>
   <si>
@@ -170,21 +170,15 @@
     <t>spreadAngle</t>
   </si>
   <si>
-    <t>delayMs</t>
-  </si>
-  <si>
-    <t>position</t>
-  </si>
-  <si>
-    <t>effectId</t>
-  </si>
-  <si>
     <t>256,256</t>
   </si>
   <si>
     <t>aircraft/self/player_aircraft_assault_001_lv01</t>
   </si>
   <si>
+    <t>中型</t>
+  </si>
+  <si>
     <t>矩形</t>
   </si>
   <si>
@@ -194,6 +188,9 @@
     <t>0.5,0.68</t>
   </si>
   <si>
+    <t>最大生命值</t>
+  </si>
+  <si>
     <t>0,98</t>
   </si>
   <si>
@@ -203,9 +200,6 @@
     <t>双侧</t>
   </si>
   <si>
-    <t>0,0</t>
-  </si>
-  <si>
     <t>aircraft/self/player_aircraft_assault_001_lv02</t>
   </si>
   <si>
@@ -221,13 +215,13 @@
     <t>500</t>
   </si>
   <si>
+    <t>右侧</t>
+  </si>
+  <si>
+    <t>66,-12</t>
+  </si>
+  <si>
     <t>左侧</t>
-  </si>
-  <si>
-    <t>66,-12</t>
-  </si>
-  <si>
-    <t>右侧</t>
   </si>
   <si>
     <t>aircraft/self/player_aircraft_assault_001_lv03</t>
@@ -360,7 +354,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -382,12 +376,6 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Carlito"/>
       <charset val="134"/>
     </font>
     <font>
@@ -726,7 +714,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -759,30 +747,6 @@
       <top style="thin">
         <color rgb="FFD9D9D9"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFD9D9D9"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFD9D9D9"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD9D9D9"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFD9D9D9"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD9D9D9"/>
-      </right>
-      <top/>
       <bottom style="thin">
         <color rgb="FFD9D9D9"/>
       </bottom>
@@ -900,153 +864,153 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0">
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="10">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="11">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="13">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="34" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="35" borderId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="34" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1066,26 +1030,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1557,7 +1501,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AD199"/>
+  <dimension ref="A1:AB199"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="7.38333333333333" style="1" customWidth="1"/>
@@ -1566,29 +1510,28 @@
     <col min="5" max="5" width="11.1333333333333" style="1" customWidth="1"/>
     <col min="6" max="6" width="17.1333333333333" style="1" customWidth="1"/>
     <col min="7" max="7" width="11.1333333333333" style="1" customWidth="1"/>
-    <col min="8" max="8" width="44.75" style="1" customWidth="1"/>
-    <col min="9" max="9" width="16" style="1" customWidth="1"/>
-    <col min="10" max="10" width="6.38333333333333" style="1" customWidth="1"/>
-    <col min="11" max="11" width="8.13333333333333" style="1" customWidth="1"/>
-    <col min="12" max="12" width="13.1333333333333" style="1" customWidth="1"/>
-    <col min="13" max="13" width="7" style="1" customWidth="1"/>
-    <col min="14" max="14" width="12.625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="7.875" style="1" customWidth="1"/>
-    <col min="16" max="16" width="11.25" style="1" customWidth="1"/>
-    <col min="17" max="17" width="11.5" style="1" customWidth="1"/>
-    <col min="18" max="18" width="12.375" style="1" customWidth="1"/>
-    <col min="19" max="19" width="14.375" style="1" customWidth="1"/>
-    <col min="20" max="20" width="16.875" style="1" customWidth="1"/>
-    <col min="21" max="21" width="9.625" style="1" customWidth="1"/>
-    <col min="22" max="22" width="12.375" style="1" customWidth="1"/>
-    <col min="23" max="23" width="13.375" style="1" customWidth="1"/>
-    <col min="24" max="26" width="9.875" style="1" customWidth="1"/>
-    <col min="27" max="27" width="35.875" style="1" customWidth="1"/>
-    <col min="28" max="28" width="7.88333333333333" style="1" customWidth="1"/>
-    <col min="29" max="29" width="28" style="1" customWidth="1"/>
+    <col min="8" max="9" width="44.75" style="1" customWidth="1"/>
+    <col min="10" max="10" width="16.5" style="1" customWidth="1"/>
+    <col min="11" max="11" width="16" style="1" customWidth="1"/>
+    <col min="12" max="12" width="6.38333333333333" style="1" customWidth="1"/>
+    <col min="13" max="13" width="8.13333333333333" style="1" customWidth="1"/>
+    <col min="14" max="14" width="13.1333333333333" style="1" customWidth="1"/>
+    <col min="15" max="15" width="11.25" style="1" customWidth="1"/>
+    <col min="16" max="16" width="6.125" style="1" customWidth="1"/>
+    <col min="17" max="17" width="7.875" style="1" customWidth="1"/>
+    <col min="18" max="18" width="11.25" style="1" customWidth="1"/>
+    <col min="19" max="19" width="11.5" style="1" customWidth="1"/>
+    <col min="20" max="20" width="12.375" style="1" customWidth="1"/>
+    <col min="21" max="21" width="14.375" style="1" customWidth="1"/>
+    <col min="22" max="22" width="16.875" style="1" customWidth="1"/>
+    <col min="23" max="23" width="9.625" style="1" customWidth="1"/>
+    <col min="24" max="24" width="12.375" style="1" customWidth="1"/>
+    <col min="25" max="25" width="13.375" style="1" customWidth="1"/>
+    <col min="26" max="26" width="7.88333333333333" style="1" customWidth="1"/>
+    <col min="27" max="27" width="28" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1" spans="1:27">
+    <row r="1" ht="20" customHeight="1" spans="1:25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1613,27 +1556,25 @@
       <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
-      <c r="N1" s="9"/>
-      <c r="O1" s="9"/>
-      <c r="P1" s="9"/>
-      <c r="Q1" s="9"/>
-      <c r="R1" s="9"/>
-      <c r="S1" s="9"/>
-      <c r="T1" s="9"/>
-      <c r="U1" s="9"/>
-      <c r="V1" s="9"/>
-      <c r="W1" s="9"/>
-      <c r="X1" s="9"/>
-      <c r="Y1" s="9"/>
-      <c r="Z1" s="9"/>
-      <c r="AA1" s="10"/>
-    </row>
-    <row r="2" ht="20" customHeight="1" spans="1:27">
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="7"/>
+      <c r="M1" s="7"/>
+      <c r="N1" s="7"/>
+      <c r="O1" s="7"/>
+      <c r="P1" s="7"/>
+      <c r="Q1" s="7"/>
+      <c r="R1" s="7"/>
+      <c r="S1" s="7"/>
+      <c r="T1" s="7"/>
+      <c r="U1" s="7"/>
+      <c r="V1" s="7"/>
+      <c r="W1" s="7"/>
+      <c r="X1" s="7"/>
+      <c r="Y1" s="7"/>
+    </row>
+    <row r="2" ht="20" customHeight="1" spans="1:25">
       <c r="A2" s="3" t="s">
         <v>8</v>
       </c>
@@ -1658,27 +1599,25 @@
       <c r="H2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9"/>
-      <c r="N2" s="9"/>
-      <c r="O2" s="9"/>
-      <c r="P2" s="9"/>
-      <c r="Q2" s="9"/>
-      <c r="R2" s="9"/>
-      <c r="S2" s="9"/>
-      <c r="T2" s="9"/>
-      <c r="U2" s="9"/>
-      <c r="V2" s="9"/>
-      <c r="W2" s="9"/>
-      <c r="X2" s="9"/>
-      <c r="Y2" s="9"/>
-      <c r="Z2" s="9"/>
-      <c r="AA2" s="10"/>
-    </row>
-    <row r="3" ht="20" customHeight="1" spans="1:27">
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="7"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="7"/>
+      <c r="O2" s="7"/>
+      <c r="P2" s="7"/>
+      <c r="Q2" s="7"/>
+      <c r="R2" s="7"/>
+      <c r="S2" s="7"/>
+      <c r="T2" s="7"/>
+      <c r="U2" s="7"/>
+      <c r="V2" s="7"/>
+      <c r="W2" s="7"/>
+      <c r="X2" s="7"/>
+      <c r="Y2" s="7"/>
+    </row>
+    <row r="3" ht="20" customHeight="1" spans="1:25">
       <c r="A3" s="2" t="s">
         <v>16</v>
       </c>
@@ -1703,27 +1642,25 @@
       <c r="H3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
-      <c r="N3" s="9"/>
-      <c r="O3" s="9"/>
-      <c r="P3" s="9"/>
-      <c r="Q3" s="9"/>
-      <c r="R3" s="9"/>
-      <c r="S3" s="9"/>
-      <c r="T3" s="9"/>
-      <c r="U3" s="9"/>
-      <c r="V3" s="9"/>
-      <c r="W3" s="9"/>
-      <c r="X3" s="9"/>
-      <c r="Y3" s="9"/>
-      <c r="Z3" s="9"/>
-      <c r="AA3" s="10"/>
-    </row>
-    <row r="4" ht="20" customHeight="1" spans="1:27">
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="7"/>
+      <c r="M3" s="7"/>
+      <c r="N3" s="7"/>
+      <c r="O3" s="7"/>
+      <c r="P3" s="7"/>
+      <c r="Q3" s="7"/>
+      <c r="R3" s="7"/>
+      <c r="S3" s="7"/>
+      <c r="T3" s="7"/>
+      <c r="U3" s="7"/>
+      <c r="V3" s="7"/>
+      <c r="W3" s="7"/>
+      <c r="X3" s="7"/>
+      <c r="Y3" s="7"/>
+    </row>
+    <row r="4" ht="20" customHeight="1" spans="1:25">
       <c r="A4" s="2" t="s">
         <v>0</v>
       </c>
@@ -1739,36 +1676,32 @@
       <c r="I4" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="10"/>
-      <c r="M4" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>23</v>
       </c>
+      <c r="L4" s="7"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="8"/>
       <c r="O4" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="P4" s="9"/>
-      <c r="Q4" s="9"/>
-      <c r="R4" s="9"/>
-      <c r="S4" s="9"/>
-      <c r="T4" s="9"/>
-      <c r="U4" s="9"/>
-      <c r="V4" s="9"/>
-      <c r="W4" s="10"/>
-      <c r="X4" s="2" t="s">
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Y4" s="9"/>
-      <c r="Z4" s="10"/>
-      <c r="AA4" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" ht="20" customHeight="1" spans="1:27">
+      <c r="R4" s="7"/>
+      <c r="S4" s="7"/>
+      <c r="T4" s="7"/>
+      <c r="U4" s="7"/>
+      <c r="V4" s="7"/>
+      <c r="W4" s="7"/>
+      <c r="X4" s="7"/>
+      <c r="Y4" s="8"/>
+    </row>
+    <row r="5" ht="20" customHeight="1" spans="1:25">
       <c r="A5" s="3" t="s">
         <v>8</v>
       </c>
@@ -1779,41 +1712,37 @@
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="10"/>
-      <c r="M5" s="3" t="s">
+      <c r="K5" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="N5" s="3" t="s">
+      <c r="L5" s="7"/>
+      <c r="M5" s="7"/>
+      <c r="N5" s="8"/>
+      <c r="O5" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="O5" s="3" t="s">
+      <c r="P5" s="3"/>
+      <c r="Q5" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="P5" s="9"/>
-      <c r="Q5" s="9"/>
-      <c r="R5" s="9"/>
-      <c r="S5" s="9"/>
-      <c r="T5" s="9"/>
-      <c r="U5" s="9"/>
-      <c r="V5" s="9"/>
-      <c r="W5" s="10"/>
-      <c r="X5" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y5" s="9"/>
-      <c r="Z5" s="10"/>
-      <c r="AA5" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1" spans="1:27">
+      <c r="R5" s="7"/>
+      <c r="S5" s="7"/>
+      <c r="T5" s="7"/>
+      <c r="U5" s="7"/>
+      <c r="V5" s="7"/>
+      <c r="W5" s="7"/>
+      <c r="X5" s="7"/>
+      <c r="Y5" s="8"/>
+    </row>
+    <row r="6" ht="20" customHeight="1" spans="1:25">
       <c r="A6" s="2" t="s">
         <v>0</v>
       </c>
@@ -1824,59 +1753,55 @@
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
-      <c r="I6" s="2" t="s">
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M6" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="N6" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="O6" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="L6" s="2" t="s">
+      <c r="P6" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2"/>
-      <c r="O6" s="2" t="s">
+      <c r="Q6" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="P6" s="2" t="s">
+      <c r="R6" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="Q6" s="2" t="s">
+      <c r="S6" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="R6" s="2" t="s">
+      <c r="T6" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="S6" s="2" t="s">
+      <c r="U6" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="T6" s="2" t="s">
+      <c r="V6" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U6" s="2" t="s">
+      <c r="W6" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="V6" s="2" t="s">
+      <c r="X6" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="W6" s="2" t="s">
+      <c r="Y6" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="X6" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="Y6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="Z6" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="AA6" s="2"/>
-    </row>
-    <row r="7" ht="20" customHeight="1" spans="1:27">
+    </row>
+    <row r="7" ht="20" customHeight="1" spans="1:25">
       <c r="A7" s="4"/>
       <c r="B7" s="4">
         <v>101</v>
@@ -1888,7 +1813,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F7" s="6">
         <v>1</v>
@@ -1897,63 +1822,59 @@
         <v>1000</v>
       </c>
       <c r="H7" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="L7" s="4"/>
+      <c r="M7" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="N7" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="J7" s="4"/>
-      <c r="K7" s="6" t="s">
+      <c r="O7" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="L7" s="6" t="s">
+      <c r="P7" s="6">
+        <v>100</v>
+      </c>
+      <c r="Q7" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="M7" s="4">
-        <v>100</v>
-      </c>
-      <c r="N7" s="6"/>
-      <c r="O7" s="6" t="s">
+      <c r="R7" s="4">
+        <v>1003</v>
+      </c>
+      <c r="S7" s="4">
+        <v>1</v>
+      </c>
+      <c r="T7" s="4">
+        <v>6</v>
+      </c>
+      <c r="U7" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="P7" s="4">
-        <v>1003</v>
-      </c>
-      <c r="Q7" s="4">
-        <v>1</v>
-      </c>
-      <c r="R7" s="4">
-        <v>6</v>
-      </c>
-      <c r="S7" s="6" t="s">
+      <c r="V7" s="4">
+        <v>50</v>
+      </c>
+      <c r="W7" s="4">
+        <v>90</v>
+      </c>
+      <c r="X7" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="T7" s="4">
-        <v>50</v>
-      </c>
-      <c r="U7" s="4">
-        <v>90</v>
-      </c>
-      <c r="V7" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="W7" s="4">
+      <c r="Y7" s="4">
         <v>0</v>
       </c>
-      <c r="X7" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="Z7" s="4">
-        <v>5001</v>
-      </c>
-      <c r="AA7" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1" spans="1:27">
+    </row>
+    <row r="8" ht="20" customHeight="1" spans="1:25">
       <c r="A8" s="4"/>
       <c r="B8" s="4">
         <v>102</v>
@@ -1965,7 +1886,7 @@
         <v>2</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F8" s="6">
         <v>4</v>
@@ -1974,63 +1895,59 @@
         <v>1250</v>
       </c>
       <c r="H8" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="L8" s="4"/>
+      <c r="M8" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="N8" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="I8" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="J8" s="4"/>
-      <c r="K8" s="4" t="s">
+      <c r="O8" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="P8" s="6">
+        <v>120</v>
+      </c>
+      <c r="Q8" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="L8" s="4" t="s">
+      <c r="R8" s="4">
+        <v>1003</v>
+      </c>
+      <c r="S8" s="4">
+        <v>1</v>
+      </c>
+      <c r="T8" s="4">
+        <v>8</v>
+      </c>
+      <c r="U8" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="M8" s="4">
-        <v>120</v>
-      </c>
-      <c r="N8" s="6"/>
-      <c r="O8" s="6" t="s">
+      <c r="V8" s="4">
+        <v>45</v>
+      </c>
+      <c r="W8" s="4">
+        <v>90</v>
+      </c>
+      <c r="X8" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="P8" s="4">
-        <v>1003</v>
-      </c>
-      <c r="Q8" s="4">
-        <v>1</v>
-      </c>
-      <c r="R8" s="4">
-        <v>8</v>
-      </c>
-      <c r="S8" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="T8" s="4">
-        <v>45</v>
-      </c>
-      <c r="U8" s="4">
-        <v>90</v>
-      </c>
-      <c r="V8" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="W8" s="4">
+      <c r="Y8" s="4">
         <v>2</v>
       </c>
-      <c r="X8" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="Z8" s="4">
-        <v>5001</v>
-      </c>
-      <c r="AA8" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1" spans="1:27">
+    </row>
+    <row r="9" ht="20" customHeight="1" spans="1:25">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
@@ -2039,45 +1956,43 @@
       <c r="F9" s="6"/>
       <c r="G9" s="5"/>
       <c r="H9" s="5"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
-      <c r="K9" s="6"/>
-      <c r="L9" s="6"/>
-      <c r="M9" s="4"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="6"/>
       <c r="N9" s="6"/>
-      <c r="O9" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="P9" s="4">
+      <c r="O9" s="4"/>
+      <c r="P9" s="6"/>
+      <c r="Q9" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="R9" s="4">
         <v>1003</v>
       </c>
-      <c r="Q9" s="4">
+      <c r="S9" s="4">
         <v>1</v>
       </c>
-      <c r="R9" s="4">
+      <c r="T9" s="4">
         <v>8</v>
       </c>
-      <c r="S9" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="T9" s="4">
+      <c r="U9" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="V9" s="4">
         <v>45</v>
       </c>
-      <c r="U9" s="4">
+      <c r="W9" s="4">
         <v>90</v>
       </c>
-      <c r="V9" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="W9" s="4">
+      <c r="X9" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y9" s="4">
         <v>2</v>
       </c>
-      <c r="X9" s="4"/>
-      <c r="Y9" s="4"/>
-      <c r="Z9" s="4"/>
-      <c r="AA9" s="5"/>
-    </row>
-    <row r="10" ht="16.5" customHeight="1" spans="1:27">
+    </row>
+    <row r="10" ht="20" customHeight="1" spans="1:25">
       <c r="A10" s="4"/>
       <c r="B10" s="4">
         <v>103</v>
@@ -2089,7 +2004,7 @@
         <v>3</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F10" s="6">
         <v>6</v>
@@ -2098,157 +2013,153 @@
         <v>1550</v>
       </c>
       <c r="H10" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="L10" s="4"/>
+      <c r="M10" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="N10" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="I10" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="J10" s="4"/>
-      <c r="K10" s="4" t="s">
+      <c r="O10" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="P10" s="6">
+        <v>150</v>
+      </c>
+      <c r="Q10" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="L10" s="4" t="s">
+      <c r="R10" s="4">
+        <v>1003</v>
+      </c>
+      <c r="S10" s="4">
+        <v>1</v>
+      </c>
+      <c r="T10" s="4">
+        <v>10</v>
+      </c>
+      <c r="U10" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="M10" s="4">
-        <v>150</v>
-      </c>
-      <c r="N10" s="6"/>
-      <c r="O10" s="6" t="s">
+      <c r="V10" s="4">
+        <v>40</v>
+      </c>
+      <c r="W10" s="4">
+        <v>90</v>
+      </c>
+      <c r="X10" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y10" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" customFormat="1" ht="20" customHeight="1" spans="1:27">
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="4"/>
+      <c r="M11" s="6"/>
+      <c r="N11" s="6"/>
+      <c r="O11" s="4"/>
+      <c r="P11" s="6"/>
+      <c r="Q11" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="P10" s="4">
+      <c r="R11" s="4">
         <v>1003</v>
       </c>
-      <c r="Q10" s="4">
+      <c r="S11" s="4">
         <v>1</v>
       </c>
-      <c r="R10" s="4">
+      <c r="T11" s="4">
         <v>10</v>
       </c>
-      <c r="S10" s="16" t="s">
+      <c r="U11" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="V11" s="4">
+        <v>40</v>
+      </c>
+      <c r="W11" s="4">
+        <v>90</v>
+      </c>
+      <c r="X11" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y11" s="4">
+        <v>2</v>
+      </c>
+      <c r="Z11" s="1"/>
+      <c r="AA11" s="1"/>
+    </row>
+    <row r="12" customFormat="1" ht="20" customHeight="1" spans="1:27">
+      <c r="A12" s="4"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="4"/>
+      <c r="L12" s="4"/>
+      <c r="M12" s="6"/>
+      <c r="N12" s="6"/>
+      <c r="O12" s="4"/>
+      <c r="P12" s="6"/>
+      <c r="Q12" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="T10" s="4">
-        <v>40</v>
-      </c>
-      <c r="U10" s="4">
+      <c r="R12" s="4">
+        <v>1001</v>
+      </c>
+      <c r="S12" s="4">
+        <v>1</v>
+      </c>
+      <c r="T12" s="4">
+        <v>3</v>
+      </c>
+      <c r="U12" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="V12" s="4">
+        <v>50</v>
+      </c>
+      <c r="W12" s="4">
         <v>90</v>
       </c>
-      <c r="V10" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="W10" s="4">
-        <v>2</v>
-      </c>
-      <c r="X10" s="4">
+      <c r="X12" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y12" s="4">
         <v>0</v>
       </c>
-      <c r="Y10" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="Z10" s="4">
-        <v>5001</v>
-      </c>
-      <c r="AA10" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" ht="16.5" customHeight="1" spans="1:27">
-      <c r="A11" s="4"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="11"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="11"/>
-      <c r="L11" s="11"/>
-      <c r="M11" s="12"/>
-      <c r="N11" s="6"/>
-      <c r="O11" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="P11" s="4">
-        <v>1003</v>
-      </c>
-      <c r="Q11" s="4">
-        <v>1</v>
-      </c>
-      <c r="R11" s="4">
-        <v>10</v>
-      </c>
-      <c r="S11" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="T11" s="4">
-        <v>40</v>
-      </c>
-      <c r="U11" s="4">
-        <v>90</v>
-      </c>
-      <c r="V11" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="W11" s="4">
-        <v>2</v>
-      </c>
-      <c r="X11" s="4"/>
-      <c r="Y11" s="4"/>
-      <c r="Z11" s="4"/>
-      <c r="AA11" s="7"/>
-    </row>
-    <row r="12" ht="16.5" customHeight="1" spans="1:27">
-      <c r="A12" s="4"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="13"/>
-      <c r="L12" s="13"/>
-      <c r="M12" s="14"/>
-      <c r="N12" s="15"/>
-      <c r="O12" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="P12" s="4">
-        <v>1001</v>
-      </c>
-      <c r="Q12" s="4">
-        <v>1</v>
-      </c>
-      <c r="R12" s="4">
-        <v>3</v>
-      </c>
-      <c r="S12" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="T12" s="4">
-        <v>50</v>
-      </c>
-      <c r="U12" s="4">
-        <v>90</v>
-      </c>
-      <c r="V12" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="W12" s="4">
-        <v>0</v>
-      </c>
-      <c r="X12" s="4"/>
-      <c r="Y12" s="4"/>
-      <c r="Z12" s="4"/>
-      <c r="AA12" s="8"/>
-    </row>
-    <row r="13" ht="16.5" customHeight="1" spans="1:27">
+      <c r="Z12" s="1"/>
+      <c r="AA12" s="1"/>
+    </row>
+    <row r="13" ht="20" customHeight="1" spans="1:25">
       <c r="A13" s="4"/>
       <c r="B13" s="4">
         <v>201</v>
@@ -2260,7 +2171,7 @@
         <v>1</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F13" s="6">
         <v>1</v>
@@ -2269,61 +2180,57 @@
         <v>1250</v>
       </c>
       <c r="H13" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="L13" s="4"/>
+      <c r="M13" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="N13" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="I13" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="J13" s="4"/>
-      <c r="K13" s="6" t="s">
+      <c r="O13" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="P13" s="6">
+        <v>150</v>
+      </c>
+      <c r="Q13" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="L13" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="M13" s="4">
-        <v>150</v>
-      </c>
-      <c r="N13" s="6"/>
-      <c r="O13" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="P13" s="4">
+      <c r="R13" s="4">
         <v>1001</v>
       </c>
-      <c r="Q13" s="4">
+      <c r="S13" s="4">
         <v>1</v>
       </c>
-      <c r="R13" s="4">
+      <c r="T13" s="4">
         <v>1</v>
       </c>
-      <c r="S13" s="6">
+      <c r="U13" s="6">
         <v>240</v>
       </c>
-      <c r="T13" s="4"/>
-      <c r="U13" s="4">
+      <c r="V13" s="4"/>
+      <c r="W13" s="4">
         <v>90</v>
       </c>
-      <c r="V13" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="W13" s="4">
+      <c r="X13" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y13" s="4">
         <v>0</v>
       </c>
-      <c r="X13" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y13" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="Z13" s="4">
-        <v>5001</v>
-      </c>
-      <c r="AA13" s="4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" ht="16.5" customHeight="1" spans="1:27">
+    </row>
+    <row r="14" ht="20" customHeight="1" spans="1:25">
       <c r="A14" s="4"/>
       <c r="B14" s="4">
         <v>202</v>
@@ -2335,7 +2242,7 @@
         <v>2</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F14" s="6">
         <v>2</v>
@@ -2344,61 +2251,57 @@
         <v>1550</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="J14" s="4"/>
-      <c r="K14" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="L14" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="M14" s="4">
+      <c r="J14" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="K14" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="L14" s="4"/>
+      <c r="M14" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="N14" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="O14" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="P14" s="6">
         <v>190</v>
       </c>
-      <c r="N14" s="6"/>
-      <c r="O14" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="P14" s="4">
+      <c r="Q14" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="R14" s="4">
         <v>1001</v>
       </c>
-      <c r="Q14" s="4">
+      <c r="S14" s="4">
         <v>1</v>
       </c>
-      <c r="R14" s="4">
+      <c r="T14" s="4">
         <v>2</v>
       </c>
-      <c r="S14" s="6">
+      <c r="U14" s="6">
         <v>240</v>
       </c>
-      <c r="T14" s="4"/>
-      <c r="U14" s="4">
+      <c r="V14" s="4"/>
+      <c r="W14" s="4">
         <v>90</v>
       </c>
-      <c r="V14" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="W14" s="4">
+      <c r="X14" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y14" s="4">
         <v>24</v>
       </c>
-      <c r="X14" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="Z14" s="4">
-        <v>5001</v>
-      </c>
-      <c r="AA14" s="4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" ht="16.5" customHeight="1" spans="1:27">
+    </row>
+    <row r="15" ht="20" customHeight="1" spans="1:25">
       <c r="A15" s="4"/>
       <c r="B15" s="4">
         <v>203</v>
@@ -2410,7 +2313,7 @@
         <v>3</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F15" s="6">
         <v>3</v>
@@ -2419,61 +2322,57 @@
         <v>1900</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="J15" s="4"/>
-      <c r="K15" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="L15" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="M15" s="4">
+        <v>79</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="K15" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="L15" s="4"/>
+      <c r="M15" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="N15" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="O15" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="P15" s="6">
         <v>240</v>
       </c>
-      <c r="N15" s="6"/>
-      <c r="O15" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="P15" s="4">
+      <c r="Q15" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="R15" s="4">
         <v>1001</v>
       </c>
-      <c r="Q15" s="4">
+      <c r="S15" s="4">
         <v>1</v>
       </c>
-      <c r="R15" s="4">
+      <c r="T15" s="4">
         <v>3</v>
       </c>
-      <c r="S15" s="6">
+      <c r="U15" s="6">
         <v>240</v>
       </c>
-      <c r="T15" s="4"/>
-      <c r="U15" s="4">
+      <c r="V15" s="4"/>
+      <c r="W15" s="4">
         <v>90</v>
       </c>
-      <c r="V15" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="W15" s="4">
+      <c r="X15" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y15" s="4">
         <v>24</v>
       </c>
-      <c r="X15" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="Z15" s="4">
-        <v>5001</v>
-      </c>
-      <c r="AA15" s="4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" ht="16.5" customHeight="1" spans="1:27">
+    </row>
+    <row r="16" ht="20" customHeight="1" spans="1:25">
       <c r="A16" s="4"/>
       <c r="B16" s="4">
         <v>301</v>
@@ -2485,7 +2384,7 @@
         <v>1</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F16" s="6">
         <v>2</v>
@@ -2494,61 +2393,57 @@
         <v>900</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="J16" s="4"/>
-      <c r="K16" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="L16" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="M16" s="4">
+        <v>81</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="L16" s="4"/>
+      <c r="M16" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="N16" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="O16" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="P16" s="6">
         <v>80</v>
       </c>
-      <c r="N16" s="6"/>
-      <c r="O16" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="P16" s="4">
+      <c r="Q16" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="R16" s="4">
         <v>1001</v>
       </c>
-      <c r="Q16" s="4">
+      <c r="S16" s="4">
         <v>1</v>
       </c>
-      <c r="R16" s="4">
+      <c r="T16" s="4">
         <v>2</v>
       </c>
-      <c r="S16" s="6">
+      <c r="U16" s="6">
         <v>240</v>
       </c>
-      <c r="T16" s="4"/>
-      <c r="U16" s="4">
+      <c r="V16" s="4"/>
+      <c r="W16" s="4">
         <v>90</v>
       </c>
-      <c r="V16" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="W16" s="4">
+      <c r="X16" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y16" s="4">
         <v>24</v>
       </c>
-      <c r="X16" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y16" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="Z16" s="4">
-        <v>5001</v>
-      </c>
-      <c r="AA16" s="4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" ht="16.5" customHeight="1" spans="1:27">
+    </row>
+    <row r="17" ht="20" customHeight="1" spans="1:25">
       <c r="A17" s="4"/>
       <c r="B17" s="4">
         <v>302</v>
@@ -2560,7 +2455,7 @@
         <v>2</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F17" s="6">
         <v>3</v>
@@ -2569,61 +2464,57 @@
         <v>1100</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="J17" s="4"/>
-      <c r="K17" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="L17" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="M17" s="4">
+        <v>83</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="L17" s="4"/>
+      <c r="M17" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="N17" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="O17" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="P17" s="6">
         <v>95</v>
       </c>
-      <c r="N17" s="6"/>
-      <c r="O17" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="P17" s="4">
+      <c r="Q17" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="R17" s="4">
         <v>1001</v>
       </c>
-      <c r="Q17" s="4">
+      <c r="S17" s="4">
         <v>1</v>
       </c>
-      <c r="R17" s="4">
+      <c r="T17" s="4">
         <v>3</v>
       </c>
-      <c r="S17" s="6">
+      <c r="U17" s="6">
         <v>240</v>
       </c>
-      <c r="T17" s="4"/>
-      <c r="U17" s="4">
+      <c r="V17" s="4"/>
+      <c r="W17" s="4">
         <v>90</v>
       </c>
-      <c r="V17" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="W17" s="4">
+      <c r="X17" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y17" s="4">
         <v>24</v>
       </c>
-      <c r="X17" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y17" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="Z17" s="4">
-        <v>5001</v>
-      </c>
-      <c r="AA17" s="4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" ht="16.5" customHeight="1" spans="1:27">
+    </row>
+    <row r="18" ht="20" customHeight="1" spans="1:25">
       <c r="A18" s="4"/>
       <c r="B18" s="4">
         <v>303</v>
@@ -2635,7 +2526,7 @@
         <v>3</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F18" s="6">
         <v>4</v>
@@ -2644,61 +2535,57 @@
         <v>1350</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="J18" s="4"/>
-      <c r="K18" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="L18" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="M18" s="4">
+        <v>85</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="K18" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="L18" s="4"/>
+      <c r="M18" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="N18" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="O18" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="P18" s="6">
         <v>115</v>
       </c>
-      <c r="N18" s="6"/>
-      <c r="O18" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="P18" s="4">
+      <c r="Q18" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="R18" s="4">
         <v>1001</v>
       </c>
-      <c r="Q18" s="4">
+      <c r="S18" s="4">
         <v>1</v>
       </c>
-      <c r="R18" s="4">
+      <c r="T18" s="4">
         <v>4</v>
       </c>
-      <c r="S18" s="6">
+      <c r="U18" s="6">
         <v>240</v>
       </c>
-      <c r="T18" s="4"/>
-      <c r="U18" s="4">
+      <c r="V18" s="4"/>
+      <c r="W18" s="4">
         <v>90</v>
       </c>
-      <c r="V18" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="W18" s="4">
+      <c r="X18" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y18" s="4">
         <v>24</v>
       </c>
-      <c r="X18" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y18" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="Z18" s="4">
-        <v>5001</v>
-      </c>
-      <c r="AA18" s="4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" ht="16.5" customHeight="1" spans="1:27">
+    </row>
+    <row r="19" ht="20" customHeight="1" spans="1:25">
       <c r="A19" s="4"/>
       <c r="B19" s="4">
         <v>304</v>
@@ -2710,7 +2597,7 @@
         <v>4</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F19" s="6">
         <v>5</v>
@@ -2719,61 +2606,57 @@
         <v>1650</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="J19" s="4"/>
-      <c r="K19" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="K19" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="L19" s="4"/>
+      <c r="M19" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="N19" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="O19" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="P19" s="6">
+        <v>140</v>
+      </c>
+      <c r="Q19" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="R19" s="4">
+        <v>1001</v>
+      </c>
+      <c r="S19" s="4">
+        <v>1</v>
+      </c>
+      <c r="T19" s="4">
+        <v>5</v>
+      </c>
+      <c r="U19" s="6">
+        <v>240</v>
+      </c>
+      <c r="V19" s="4"/>
+      <c r="W19" s="4">
         <v>90</v>
       </c>
-      <c r="L19" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="M19" s="4">
-        <v>140</v>
-      </c>
-      <c r="N19" s="6"/>
-      <c r="O19" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="P19" s="4">
-        <v>1001</v>
-      </c>
-      <c r="Q19" s="4">
-        <v>1</v>
-      </c>
-      <c r="R19" s="4">
-        <v>5</v>
-      </c>
-      <c r="S19" s="6">
-        <v>240</v>
-      </c>
-      <c r="T19" s="4"/>
-      <c r="U19" s="4">
-        <v>90</v>
-      </c>
-      <c r="V19" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="W19" s="4">
+      <c r="X19" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y19" s="4">
         <v>24</v>
       </c>
-      <c r="X19" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y19" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="Z19" s="4">
-        <v>5001</v>
-      </c>
-      <c r="AA19" s="4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" ht="16.5" customHeight="1" spans="1:27">
+    </row>
+    <row r="20" ht="20" customHeight="1" spans="1:25">
       <c r="A20" s="4"/>
       <c r="B20" s="4">
         <v>401</v>
@@ -2785,7 +2668,7 @@
         <v>1</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F20" s="6">
         <v>3</v>
@@ -2794,61 +2677,57 @@
         <v>1100</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="J20" s="4"/>
-      <c r="K20" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="L20" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="M20" s="4">
+        <v>89</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="K20" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="L20" s="4"/>
+      <c r="M20" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="N20" s="6"/>
-      <c r="O20" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="P20" s="4">
+      <c r="N20" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="O20" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="P20" s="6">
+        <v>90</v>
+      </c>
+      <c r="Q20" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="R20" s="4">
         <v>1001</v>
       </c>
-      <c r="Q20" s="4">
+      <c r="S20" s="4">
         <v>1</v>
       </c>
-      <c r="R20" s="4">
+      <c r="T20" s="4">
         <v>3</v>
       </c>
-      <c r="S20" s="6">
+      <c r="U20" s="6">
         <v>240</v>
       </c>
-      <c r="T20" s="4"/>
-      <c r="U20" s="4">
+      <c r="V20" s="4"/>
+      <c r="W20" s="4">
         <v>90</v>
       </c>
-      <c r="V20" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="W20" s="4">
+      <c r="X20" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y20" s="4">
         <v>24</v>
       </c>
-      <c r="X20" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y20" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="Z20" s="4">
-        <v>5001</v>
-      </c>
-      <c r="AA20" s="4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" ht="16.5" customHeight="1" spans="1:27">
+    </row>
+    <row r="21" ht="20" customHeight="1" spans="1:25">
       <c r="A21" s="4"/>
       <c r="B21" s="4">
         <v>402</v>
@@ -2860,7 +2739,7 @@
         <v>2</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F21" s="6">
         <v>5</v>
@@ -2869,61 +2748,57 @@
         <v>1350</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="J21" s="4"/>
-      <c r="K21" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="L21" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="M21" s="4">
+        <v>91</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="K21" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="L21" s="4"/>
+      <c r="M21" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="N21" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="O21" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="P21" s="6">
         <v>110</v>
       </c>
-      <c r="N21" s="6"/>
-      <c r="O21" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="P21" s="4">
+      <c r="Q21" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="R21" s="4">
         <v>1001</v>
       </c>
-      <c r="Q21" s="4">
+      <c r="S21" s="4">
         <v>1</v>
       </c>
-      <c r="R21" s="4">
+      <c r="T21" s="4">
         <v>5</v>
       </c>
-      <c r="S21" s="6">
+      <c r="U21" s="6">
         <v>240</v>
       </c>
-      <c r="T21" s="4"/>
-      <c r="U21" s="4">
+      <c r="V21" s="4"/>
+      <c r="W21" s="4">
         <v>90</v>
       </c>
-      <c r="V21" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="W21" s="4">
+      <c r="X21" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y21" s="4">
         <v>24</v>
       </c>
-      <c r="X21" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y21" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="Z21" s="4">
-        <v>5001</v>
-      </c>
-      <c r="AA21" s="4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" ht="16.5" customHeight="1" spans="1:27">
+    </row>
+    <row r="22" ht="20" customHeight="1" spans="1:25">
       <c r="A22" s="4"/>
       <c r="B22" s="4">
         <v>403</v>
@@ -2935,7 +2810,7 @@
         <v>3</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F22" s="6">
         <v>7</v>
@@ -2944,61 +2819,57 @@
         <v>1650</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="J22" s="4"/>
-      <c r="K22" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="L22" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="M22" s="4">
+        <v>93</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="K22" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="L22" s="4"/>
+      <c r="M22" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="N22" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="O22" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="P22" s="6">
         <v>135</v>
       </c>
-      <c r="N22" s="6"/>
-      <c r="O22" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="P22" s="4">
+      <c r="Q22" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="R22" s="4">
         <v>1001</v>
       </c>
-      <c r="Q22" s="4">
+      <c r="S22" s="4">
         <v>1</v>
       </c>
-      <c r="R22" s="4">
+      <c r="T22" s="4">
         <v>7</v>
       </c>
-      <c r="S22" s="6">
+      <c r="U22" s="6">
         <v>240</v>
       </c>
-      <c r="T22" s="4"/>
-      <c r="U22" s="4">
+      <c r="V22" s="4"/>
+      <c r="W22" s="4">
         <v>90</v>
       </c>
-      <c r="V22" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="W22" s="4">
+      <c r="X22" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y22" s="4">
         <v>24</v>
       </c>
-      <c r="X22" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y22" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="Z22" s="4">
-        <v>5001</v>
-      </c>
-      <c r="AA22" s="4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" ht="16.5" customHeight="1" spans="1:27">
+    </row>
+    <row r="23" ht="20" customHeight="1" spans="1:25">
       <c r="A23" s="4"/>
       <c r="B23" s="4">
         <v>404</v>
@@ -3010,7 +2881,7 @@
         <v>4</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F23" s="6">
         <v>9</v>
@@ -3019,61 +2890,57 @@
         <v>2000</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="J23" s="4"/>
-      <c r="K23" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="L23" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="M23" s="4">
+        <v>95</v>
+      </c>
+      <c r="J23" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="K23" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="L23" s="4"/>
+      <c r="M23" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="N23" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="O23" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="P23" s="6">
         <v>165</v>
       </c>
-      <c r="N23" s="6"/>
-      <c r="O23" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="P23" s="4">
+      <c r="Q23" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="R23" s="4">
         <v>1001</v>
       </c>
-      <c r="Q23" s="4">
+      <c r="S23" s="4">
         <v>1</v>
       </c>
-      <c r="R23" s="4">
+      <c r="T23" s="4">
         <v>9</v>
       </c>
-      <c r="S23" s="6">
+      <c r="U23" s="6">
         <v>240</v>
       </c>
-      <c r="T23" s="4"/>
-      <c r="U23" s="4">
+      <c r="V23" s="4"/>
+      <c r="W23" s="4">
         <v>90</v>
       </c>
-      <c r="V23" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="W23" s="4">
+      <c r="X23" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y23" s="4">
         <v>24</v>
       </c>
-      <c r="X23" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y23" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="Z23" s="4">
-        <v>5001</v>
-      </c>
-      <c r="AA23" s="4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" ht="16.5" customHeight="1" spans="1:27">
+    </row>
+    <row r="24" ht="20" customHeight="1" spans="1:25">
       <c r="A24" s="4"/>
       <c r="B24" s="4">
         <v>501</v>
@@ -3085,7 +2952,7 @@
         <v>1</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F24" s="6">
         <v>1</v>
@@ -3094,61 +2961,57 @@
         <v>1350</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="J24" s="4"/>
-      <c r="K24" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="L24" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="M24" s="4">
+        <v>97</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="K24" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="L24" s="4"/>
+      <c r="M24" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="N24" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="O24" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="P24" s="6">
         <v>95</v>
       </c>
-      <c r="N24" s="6"/>
-      <c r="O24" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="P24" s="4">
+      <c r="Q24" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="R24" s="4">
         <v>1001</v>
       </c>
-      <c r="Q24" s="4">
+      <c r="S24" s="4">
         <v>1</v>
       </c>
-      <c r="R24" s="4">
+      <c r="T24" s="4">
         <v>1</v>
       </c>
-      <c r="S24" s="6">
+      <c r="U24" s="6">
         <v>240</v>
       </c>
-      <c r="T24" s="4"/>
-      <c r="U24" s="4">
+      <c r="V24" s="4"/>
+      <c r="W24" s="4">
         <v>90</v>
       </c>
-      <c r="V24" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="W24" s="4">
+      <c r="X24" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y24" s="4">
         <v>0</v>
       </c>
-      <c r="X24" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y24" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="Z24" s="4">
-        <v>5001</v>
-      </c>
-      <c r="AA24" s="4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" ht="16.5" customHeight="1" spans="1:27">
+    </row>
+    <row r="25" ht="20" customHeight="1" spans="1:25">
       <c r="A25" s="4"/>
       <c r="B25" s="4">
         <v>502</v>
@@ -3160,7 +3023,7 @@
         <v>2</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F25" s="6">
         <v>1</v>
@@ -3169,61 +3032,57 @@
         <v>1650</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="J25" s="4"/>
-      <c r="K25" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="L25" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="M25" s="4">
+        <v>99</v>
+      </c>
+      <c r="J25" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="K25" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="L25" s="4"/>
+      <c r="M25" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="N25" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="O25" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="P25" s="6">
         <v>115</v>
       </c>
-      <c r="N25" s="6"/>
-      <c r="O25" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="P25" s="4">
+      <c r="Q25" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="R25" s="4">
         <v>1001</v>
       </c>
-      <c r="Q25" s="4">
+      <c r="S25" s="4">
         <v>1</v>
       </c>
-      <c r="R25" s="4">
+      <c r="T25" s="4">
         <v>1</v>
       </c>
-      <c r="S25" s="6">
+      <c r="U25" s="6">
         <v>240</v>
       </c>
-      <c r="T25" s="4"/>
-      <c r="U25" s="4">
+      <c r="V25" s="4"/>
+      <c r="W25" s="4">
         <v>90</v>
       </c>
-      <c r="V25" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="W25" s="4">
+      <c r="X25" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y25" s="4">
         <v>0</v>
       </c>
-      <c r="X25" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y25" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="Z25" s="4">
-        <v>5001</v>
-      </c>
-      <c r="AA25" s="4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" ht="16.5" customHeight="1" spans="1:27">
+    </row>
+    <row r="26" ht="20" customHeight="1" spans="1:25">
       <c r="A26" s="4"/>
       <c r="B26" s="4">
         <v>503</v>
@@ -3235,7 +3094,7 @@
         <v>3</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F26" s="6">
         <v>2</v>
@@ -3244,61 +3103,57 @@
         <v>2000</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="J26" s="4"/>
-      <c r="K26" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="L26" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="M26" s="4">
+        <v>101</v>
+      </c>
+      <c r="J26" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="K26" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="L26" s="4"/>
+      <c r="M26" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="N26" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="O26" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="P26" s="6">
         <v>145</v>
       </c>
-      <c r="N26" s="6"/>
-      <c r="O26" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="P26" s="4">
+      <c r="Q26" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="R26" s="4">
         <v>1001</v>
       </c>
-      <c r="Q26" s="4">
+      <c r="S26" s="4">
         <v>1</v>
       </c>
-      <c r="R26" s="4">
+      <c r="T26" s="4">
         <v>2</v>
       </c>
-      <c r="S26" s="6">
+      <c r="U26" s="6">
         <v>240</v>
       </c>
-      <c r="T26" s="4"/>
-      <c r="U26" s="4">
+      <c r="V26" s="4"/>
+      <c r="W26" s="4">
         <v>90</v>
       </c>
-      <c r="V26" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="W26" s="4">
+      <c r="X26" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y26" s="4">
         <v>24</v>
       </c>
-      <c r="X26" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y26" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="Z26" s="4">
-        <v>5001</v>
-      </c>
-      <c r="AA26" s="4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" ht="16.5" customHeight="1" spans="1:27">
+    </row>
+    <row r="27" ht="20" customHeight="1" spans="1:25">
       <c r="A27" s="4"/>
       <c r="B27" s="4">
         <v>504</v>
@@ -3310,7 +3165,7 @@
         <v>4</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F27" s="6">
         <v>2</v>
@@ -3319,787 +3174,777 @@
         <v>2400</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="J27" s="4"/>
-      <c r="K27" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="L27" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="M27" s="4">
+        <v>103</v>
+      </c>
+      <c r="J27" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="K27" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="L27" s="4"/>
+      <c r="M27" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="N27" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="O27" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="P27" s="6">
         <v>180</v>
       </c>
-      <c r="N27" s="6"/>
-      <c r="O27" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="P27" s="4">
+      <c r="Q27" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="R27" s="4">
         <v>1001</v>
       </c>
-      <c r="Q27" s="4">
+      <c r="S27" s="4">
         <v>1</v>
       </c>
-      <c r="R27" s="4">
+      <c r="T27" s="4">
         <v>2</v>
       </c>
-      <c r="S27" s="6">
+      <c r="U27" s="6">
         <v>240</v>
       </c>
-      <c r="T27" s="4"/>
-      <c r="U27" s="4">
+      <c r="V27" s="4"/>
+      <c r="W27" s="4">
         <v>90</v>
       </c>
-      <c r="V27" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="W27" s="4">
+      <c r="X27" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y27" s="4">
         <v>24</v>
       </c>
-      <c r="X27" s="4">
-        <v>0</v>
-      </c>
-      <c r="Y27" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="Z27" s="4">
-        <v>5001</v>
-      </c>
-      <c r="AA27" s="4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" ht="16.5" customHeight="1" spans="14:30">
-      <c r="N28"/>
-      <c r="O28"/>
+    </row>
+    <row r="28" ht="16.5" customHeight="1" spans="16:28">
+      <c r="P28"/>
+      <c r="Q28"/>
+      <c r="Z28" s="4"/>
+      <c r="AA28" s="4"/>
       <c r="AB28" s="4"/>
-      <c r="AC28" s="4"/>
-      <c r="AD28" s="4"/>
-    </row>
-    <row r="29" ht="16.5" customHeight="1" spans="14:30">
-      <c r="N29"/>
-      <c r="O29"/>
+    </row>
+    <row r="29" ht="16.5" customHeight="1" spans="16:28">
+      <c r="P29"/>
+      <c r="Q29"/>
+      <c r="Z29" s="4"/>
+      <c r="AA29" s="4"/>
       <c r="AB29" s="4"/>
-      <c r="AC29" s="4"/>
-      <c r="AD29" s="4"/>
-    </row>
-    <row r="30" spans="14:15">
-      <c r="N30"/>
-      <c r="O30"/>
-    </row>
-    <row r="31" spans="14:15">
-      <c r="N31"/>
-      <c r="O31"/>
-    </row>
-    <row r="32" spans="14:15">
-      <c r="N32"/>
-      <c r="O32"/>
-    </row>
-    <row r="33" spans="14:15">
-      <c r="N33"/>
-      <c r="O33"/>
-    </row>
-    <row r="34" spans="14:15">
-      <c r="N34"/>
-      <c r="O34"/>
-    </row>
-    <row r="35" spans="14:15">
-      <c r="N35"/>
-      <c r="O35"/>
-    </row>
-    <row r="36" spans="14:15">
-      <c r="N36"/>
-      <c r="O36"/>
-    </row>
-    <row r="37" spans="14:15">
-      <c r="N37"/>
-      <c r="O37"/>
-    </row>
-    <row r="38" spans="14:15">
-      <c r="N38"/>
-      <c r="O38"/>
-    </row>
-    <row r="39" spans="14:15">
-      <c r="N39"/>
-      <c r="O39"/>
-    </row>
-    <row r="40" spans="14:15">
-      <c r="N40"/>
-      <c r="O40"/>
-    </row>
-    <row r="41" spans="14:15">
-      <c r="N41"/>
-      <c r="O41"/>
-    </row>
-    <row r="42" spans="14:15">
-      <c r="N42"/>
-      <c r="O42"/>
-    </row>
-    <row r="43" spans="14:15">
-      <c r="N43"/>
-      <c r="O43"/>
-    </row>
-    <row r="44" spans="14:15">
-      <c r="N44"/>
-      <c r="O44"/>
-    </row>
-    <row r="45" spans="14:15">
-      <c r="N45"/>
-      <c r="O45"/>
-    </row>
-    <row r="46" spans="14:15">
-      <c r="N46"/>
-      <c r="O46"/>
-    </row>
-    <row r="47" spans="14:15">
-      <c r="N47"/>
-      <c r="O47"/>
-    </row>
-    <row r="48" spans="14:15">
-      <c r="N48"/>
-      <c r="O48"/>
-    </row>
-    <row r="49" spans="14:15">
-      <c r="N49"/>
-      <c r="O49"/>
-    </row>
-    <row r="50" spans="14:15">
-      <c r="N50"/>
-      <c r="O50"/>
-    </row>
-    <row r="51" spans="14:15">
-      <c r="N51"/>
-      <c r="O51"/>
-    </row>
-    <row r="52" spans="14:15">
-      <c r="N52"/>
-      <c r="O52"/>
-    </row>
-    <row r="53" spans="14:15">
-      <c r="N53"/>
-      <c r="O53"/>
-    </row>
-    <row r="54" spans="14:15">
-      <c r="N54"/>
-      <c r="O54"/>
-    </row>
-    <row r="55" spans="14:15">
-      <c r="N55"/>
-      <c r="O55"/>
-    </row>
-    <row r="56" spans="14:15">
-      <c r="N56"/>
-      <c r="O56"/>
-    </row>
-    <row r="57" spans="14:15">
-      <c r="N57"/>
-      <c r="O57"/>
-    </row>
-    <row r="58" spans="14:15">
-      <c r="N58"/>
-      <c r="O58"/>
-    </row>
-    <row r="59" spans="14:15">
-      <c r="N59"/>
-      <c r="O59"/>
-    </row>
-    <row r="60" spans="14:15">
-      <c r="N60"/>
-      <c r="O60"/>
-    </row>
-    <row r="61" spans="14:15">
-      <c r="N61"/>
-      <c r="O61"/>
-    </row>
-    <row r="62" spans="14:15">
-      <c r="N62"/>
-      <c r="O62"/>
-    </row>
-    <row r="63" spans="14:15">
-      <c r="N63"/>
-      <c r="O63"/>
-    </row>
-    <row r="64" spans="14:15">
-      <c r="N64"/>
-      <c r="O64"/>
-    </row>
-    <row r="65" spans="14:15">
-      <c r="N65"/>
-      <c r="O65"/>
-    </row>
-    <row r="66" spans="14:15">
-      <c r="N66"/>
-      <c r="O66"/>
-    </row>
-    <row r="67" spans="14:15">
-      <c r="N67"/>
-      <c r="O67"/>
-    </row>
-    <row r="68" spans="14:15">
-      <c r="N68"/>
-      <c r="O68"/>
-    </row>
-    <row r="69" spans="14:15">
-      <c r="N69"/>
-      <c r="O69"/>
-    </row>
-    <row r="70" spans="14:15">
-      <c r="N70"/>
-      <c r="O70"/>
-    </row>
-    <row r="71" spans="14:15">
-      <c r="N71"/>
-      <c r="O71"/>
-    </row>
-    <row r="72" spans="14:15">
-      <c r="N72"/>
-      <c r="O72"/>
-    </row>
-    <row r="73" spans="14:15">
-      <c r="N73"/>
-      <c r="O73"/>
-    </row>
-    <row r="74" spans="14:15">
-      <c r="N74"/>
-      <c r="O74"/>
-    </row>
-    <row r="75" spans="14:15">
-      <c r="N75"/>
-      <c r="O75"/>
-    </row>
-    <row r="76" spans="14:15">
-      <c r="N76"/>
-      <c r="O76"/>
-    </row>
-    <row r="77" spans="14:15">
-      <c r="N77"/>
-      <c r="O77"/>
-    </row>
-    <row r="78" spans="14:15">
-      <c r="N78"/>
-      <c r="O78"/>
-    </row>
-    <row r="79" spans="14:15">
-      <c r="N79"/>
-      <c r="O79"/>
-    </row>
-    <row r="80" spans="14:15">
-      <c r="N80"/>
-      <c r="O80"/>
-    </row>
-    <row r="81" spans="14:15">
-      <c r="N81"/>
-      <c r="O81"/>
-    </row>
-    <row r="82" spans="14:15">
-      <c r="N82"/>
-      <c r="O82"/>
-    </row>
-    <row r="83" spans="14:15">
-      <c r="N83"/>
-      <c r="O83"/>
-    </row>
-    <row r="84" spans="14:15">
-      <c r="N84"/>
-      <c r="O84"/>
-    </row>
-    <row r="85" spans="14:15">
-      <c r="N85"/>
-      <c r="O85"/>
-    </row>
-    <row r="86" spans="14:15">
-      <c r="N86"/>
-      <c r="O86"/>
-    </row>
-    <row r="87" spans="14:15">
-      <c r="N87"/>
-      <c r="O87"/>
-    </row>
-    <row r="88" spans="14:15">
-      <c r="N88"/>
-      <c r="O88"/>
-    </row>
-    <row r="89" spans="14:15">
-      <c r="N89"/>
-      <c r="O89"/>
-    </row>
-    <row r="90" spans="14:15">
-      <c r="N90"/>
-      <c r="O90"/>
-    </row>
-    <row r="91" spans="14:15">
-      <c r="N91"/>
-      <c r="O91"/>
-    </row>
-    <row r="92" spans="14:15">
-      <c r="N92"/>
-      <c r="O92"/>
-    </row>
-    <row r="93" spans="14:15">
-      <c r="N93"/>
-      <c r="O93"/>
-    </row>
-    <row r="94" spans="14:15">
-      <c r="N94"/>
-      <c r="O94"/>
-    </row>
-    <row r="95" spans="14:15">
-      <c r="N95"/>
-      <c r="O95"/>
-    </row>
-    <row r="96" spans="14:15">
-      <c r="N96"/>
-      <c r="O96"/>
-    </row>
-    <row r="97" spans="14:15">
-      <c r="N97"/>
-      <c r="O97"/>
-    </row>
-    <row r="98" spans="14:15">
-      <c r="N98"/>
-      <c r="O98"/>
-    </row>
-    <row r="99" spans="14:15">
-      <c r="N99"/>
-      <c r="O99"/>
-    </row>
-    <row r="100" spans="14:15">
-      <c r="N100"/>
-      <c r="O100"/>
-    </row>
-    <row r="101" spans="14:15">
-      <c r="N101"/>
-      <c r="O101"/>
-    </row>
-    <row r="102" spans="14:15">
-      <c r="N102"/>
-      <c r="O102"/>
-    </row>
-    <row r="103" spans="14:15">
-      <c r="N103"/>
-      <c r="O103"/>
-    </row>
-    <row r="104" spans="14:15">
-      <c r="N104"/>
-      <c r="O104"/>
-    </row>
-    <row r="105" spans="14:15">
-      <c r="N105"/>
-      <c r="O105"/>
-    </row>
-    <row r="106" spans="14:15">
-      <c r="N106"/>
-      <c r="O106"/>
-    </row>
-    <row r="107" spans="14:15">
-      <c r="N107"/>
-      <c r="O107"/>
-    </row>
-    <row r="108" spans="14:15">
-      <c r="N108"/>
-      <c r="O108"/>
-    </row>
-    <row r="109" spans="14:15">
-      <c r="N109"/>
-      <c r="O109"/>
-    </row>
-    <row r="110" spans="14:15">
-      <c r="N110"/>
-      <c r="O110"/>
-    </row>
-    <row r="111" spans="14:15">
-      <c r="N111"/>
-      <c r="O111"/>
-    </row>
-    <row r="112" spans="14:15">
-      <c r="N112"/>
-      <c r="O112"/>
-    </row>
-    <row r="113" spans="14:15">
-      <c r="N113"/>
-      <c r="O113"/>
-    </row>
-    <row r="114" spans="14:15">
-      <c r="N114"/>
-      <c r="O114"/>
-    </row>
-    <row r="115" spans="14:15">
-      <c r="N115"/>
-      <c r="O115"/>
-    </row>
-    <row r="116" spans="14:15">
-      <c r="N116"/>
-      <c r="O116"/>
-    </row>
-    <row r="117" spans="14:15">
-      <c r="N117"/>
-      <c r="O117"/>
-    </row>
-    <row r="118" spans="14:15">
-      <c r="N118"/>
-      <c r="O118"/>
-    </row>
-    <row r="119" spans="14:15">
-      <c r="N119"/>
-      <c r="O119"/>
-    </row>
-    <row r="120" spans="14:15">
-      <c r="N120"/>
-      <c r="O120"/>
-    </row>
-    <row r="121" spans="14:15">
-      <c r="N121"/>
-      <c r="O121"/>
-    </row>
-    <row r="122" spans="14:15">
-      <c r="N122"/>
-      <c r="O122"/>
-    </row>
-    <row r="123" spans="14:15">
-      <c r="N123"/>
-      <c r="O123"/>
-    </row>
-    <row r="124" spans="14:15">
-      <c r="N124"/>
-      <c r="O124"/>
-    </row>
-    <row r="125" spans="14:15">
-      <c r="N125"/>
-      <c r="O125"/>
-    </row>
-    <row r="126" spans="14:15">
-      <c r="N126"/>
-      <c r="O126"/>
-    </row>
-    <row r="127" spans="14:15">
-      <c r="N127"/>
-      <c r="O127"/>
-    </row>
-    <row r="128" spans="14:15">
-      <c r="N128"/>
-      <c r="O128"/>
-    </row>
-    <row r="129" spans="14:15">
-      <c r="N129"/>
-      <c r="O129"/>
-    </row>
-    <row r="130" spans="14:15">
-      <c r="N130"/>
-      <c r="O130"/>
-    </row>
-    <row r="131" spans="14:15">
-      <c r="N131"/>
-      <c r="O131"/>
-    </row>
-    <row r="132" spans="14:15">
-      <c r="N132"/>
-      <c r="O132"/>
-    </row>
-    <row r="133" spans="14:15">
-      <c r="N133"/>
-      <c r="O133"/>
-    </row>
-    <row r="134" spans="14:15">
-      <c r="N134"/>
-      <c r="O134"/>
-    </row>
-    <row r="135" spans="14:15">
-      <c r="N135"/>
-      <c r="O135"/>
-    </row>
-    <row r="136" spans="14:15">
-      <c r="N136"/>
-      <c r="O136"/>
-    </row>
-    <row r="137" spans="14:15">
-      <c r="N137"/>
-      <c r="O137"/>
-    </row>
-    <row r="138" spans="14:15">
-      <c r="N138"/>
-      <c r="O138"/>
-    </row>
-    <row r="139" spans="14:15">
-      <c r="N139"/>
-      <c r="O139"/>
-    </row>
-    <row r="140" spans="14:15">
-      <c r="N140"/>
-      <c r="O140"/>
-    </row>
-    <row r="141" spans="14:15">
-      <c r="N141"/>
-      <c r="O141"/>
-    </row>
-    <row r="142" spans="14:15">
-      <c r="N142"/>
-      <c r="O142"/>
-    </row>
-    <row r="143" spans="14:15">
-      <c r="N143"/>
-      <c r="O143"/>
-    </row>
-    <row r="144" spans="14:15">
-      <c r="N144"/>
-      <c r="O144"/>
-    </row>
-    <row r="145" spans="14:15">
-      <c r="N145"/>
-      <c r="O145"/>
-    </row>
-    <row r="146" spans="14:15">
-      <c r="N146"/>
-      <c r="O146"/>
-    </row>
-    <row r="147" spans="14:15">
-      <c r="N147"/>
-      <c r="O147"/>
-    </row>
-    <row r="148" spans="14:15">
-      <c r="N148"/>
-      <c r="O148"/>
-    </row>
-    <row r="149" spans="14:15">
-      <c r="N149"/>
-      <c r="O149"/>
-    </row>
-    <row r="150" spans="14:15">
-      <c r="N150"/>
-      <c r="O150"/>
-    </row>
-    <row r="151" spans="14:15">
-      <c r="N151"/>
-      <c r="O151"/>
-    </row>
-    <row r="152" spans="14:15">
-      <c r="N152"/>
-      <c r="O152"/>
-    </row>
-    <row r="153" spans="14:15">
-      <c r="N153"/>
-      <c r="O153"/>
-    </row>
-    <row r="154" spans="14:15">
-      <c r="N154"/>
-      <c r="O154"/>
-    </row>
-    <row r="155" spans="14:15">
-      <c r="N155"/>
-      <c r="O155"/>
-    </row>
-    <row r="156" spans="14:15">
-      <c r="N156"/>
-      <c r="O156"/>
-    </row>
-    <row r="157" spans="14:15">
-      <c r="N157"/>
-      <c r="O157"/>
-    </row>
-    <row r="158" spans="14:15">
-      <c r="N158"/>
-      <c r="O158"/>
-    </row>
-    <row r="159" spans="14:15">
-      <c r="N159"/>
-      <c r="O159"/>
-    </row>
-    <row r="160" spans="14:15">
-      <c r="N160"/>
-      <c r="O160"/>
-    </row>
-    <row r="161" spans="14:15">
-      <c r="N161"/>
-      <c r="O161"/>
-    </row>
-    <row r="162" spans="14:15">
-      <c r="N162"/>
-      <c r="O162"/>
-    </row>
-    <row r="163" spans="14:15">
-      <c r="N163"/>
-      <c r="O163"/>
-    </row>
-    <row r="164" spans="14:15">
-      <c r="N164"/>
-      <c r="O164"/>
-    </row>
-    <row r="165" spans="14:15">
-      <c r="N165"/>
-      <c r="O165"/>
-    </row>
-    <row r="166" spans="14:15">
-      <c r="N166"/>
-      <c r="O166"/>
-    </row>
-    <row r="167" spans="14:15">
-      <c r="N167"/>
-      <c r="O167"/>
-    </row>
-    <row r="168" spans="14:15">
-      <c r="N168"/>
-      <c r="O168"/>
-    </row>
-    <row r="169" spans="14:15">
-      <c r="N169"/>
-      <c r="O169"/>
-    </row>
-    <row r="170" spans="14:15">
-      <c r="N170"/>
-      <c r="O170"/>
-    </row>
-    <row r="171" spans="14:15">
-      <c r="N171"/>
-      <c r="O171"/>
-    </row>
-    <row r="172" spans="14:15">
-      <c r="N172"/>
-      <c r="O172"/>
-    </row>
-    <row r="173" spans="14:15">
-      <c r="N173"/>
-      <c r="O173"/>
-    </row>
-    <row r="174" spans="14:15">
-      <c r="N174"/>
-      <c r="O174"/>
-    </row>
-    <row r="175" spans="14:15">
-      <c r="N175"/>
-      <c r="O175"/>
-    </row>
-    <row r="176" spans="14:15">
-      <c r="N176"/>
-      <c r="O176"/>
-    </row>
-    <row r="177" spans="14:15">
-      <c r="N177"/>
-      <c r="O177"/>
-    </row>
-    <row r="178" spans="14:15">
-      <c r="N178"/>
-      <c r="O178"/>
-    </row>
-    <row r="179" spans="14:15">
-      <c r="N179"/>
-      <c r="O179"/>
-    </row>
-    <row r="180" spans="14:15">
-      <c r="N180"/>
-      <c r="O180"/>
-    </row>
-    <row r="181" spans="14:15">
-      <c r="N181"/>
-      <c r="O181"/>
-    </row>
-    <row r="182" spans="14:15">
-      <c r="N182"/>
-      <c r="O182"/>
-    </row>
-    <row r="183" spans="14:15">
-      <c r="N183"/>
-      <c r="O183"/>
-    </row>
-    <row r="184" spans="14:15">
-      <c r="N184"/>
-      <c r="O184"/>
-    </row>
-    <row r="185" spans="14:15">
-      <c r="N185"/>
-      <c r="O185"/>
-    </row>
-    <row r="186" spans="14:15">
-      <c r="N186"/>
-      <c r="O186"/>
-    </row>
-    <row r="187" spans="14:15">
-      <c r="N187"/>
-      <c r="O187"/>
-    </row>
-    <row r="188" spans="14:15">
-      <c r="N188"/>
-      <c r="O188"/>
-    </row>
-    <row r="189" spans="14:15">
-      <c r="N189"/>
-      <c r="O189"/>
-    </row>
-    <row r="190" spans="14:15">
-      <c r="N190"/>
-      <c r="O190"/>
-    </row>
-    <row r="191" spans="14:15">
-      <c r="N191"/>
-      <c r="O191"/>
-    </row>
-    <row r="192" spans="14:15">
-      <c r="N192"/>
-      <c r="O192"/>
-    </row>
-    <row r="193" spans="14:15">
-      <c r="N193"/>
-      <c r="O193"/>
-    </row>
-    <row r="194" spans="14:15">
-      <c r="N194"/>
-      <c r="O194"/>
-    </row>
-    <row r="195" spans="14:15">
-      <c r="N195"/>
-      <c r="O195"/>
-    </row>
-    <row r="196" spans="14:15">
-      <c r="N196"/>
-      <c r="O196"/>
-    </row>
-    <row r="197" spans="14:15">
-      <c r="N197"/>
-      <c r="O197"/>
-    </row>
-    <row r="198" spans="14:15">
-      <c r="N198"/>
-      <c r="O198"/>
-    </row>
-    <row r="199" spans="14:15">
-      <c r="N199"/>
-      <c r="O199"/>
+    </row>
+    <row r="30" spans="16:17">
+      <c r="P30"/>
+      <c r="Q30"/>
+    </row>
+    <row r="31" spans="16:17">
+      <c r="P31"/>
+      <c r="Q31"/>
+    </row>
+    <row r="32" spans="16:17">
+      <c r="P32"/>
+      <c r="Q32"/>
+    </row>
+    <row r="33" spans="16:17">
+      <c r="P33"/>
+      <c r="Q33"/>
+    </row>
+    <row r="34" spans="16:17">
+      <c r="P34"/>
+      <c r="Q34"/>
+    </row>
+    <row r="35" spans="16:17">
+      <c r="P35"/>
+      <c r="Q35"/>
+    </row>
+    <row r="36" spans="16:17">
+      <c r="P36"/>
+      <c r="Q36"/>
+    </row>
+    <row r="37" spans="16:17">
+      <c r="P37"/>
+      <c r="Q37"/>
+    </row>
+    <row r="38" spans="16:17">
+      <c r="P38"/>
+      <c r="Q38"/>
+    </row>
+    <row r="39" spans="16:17">
+      <c r="P39"/>
+      <c r="Q39"/>
+    </row>
+    <row r="40" spans="16:17">
+      <c r="P40"/>
+      <c r="Q40"/>
+    </row>
+    <row r="41" spans="16:17">
+      <c r="P41"/>
+      <c r="Q41"/>
+    </row>
+    <row r="42" spans="16:17">
+      <c r="P42"/>
+      <c r="Q42"/>
+    </row>
+    <row r="43" spans="16:17">
+      <c r="P43"/>
+      <c r="Q43"/>
+    </row>
+    <row r="44" spans="16:17">
+      <c r="P44"/>
+      <c r="Q44"/>
+    </row>
+    <row r="45" spans="16:17">
+      <c r="P45"/>
+      <c r="Q45"/>
+    </row>
+    <row r="46" spans="16:17">
+      <c r="P46"/>
+      <c r="Q46"/>
+    </row>
+    <row r="47" spans="16:17">
+      <c r="P47"/>
+      <c r="Q47"/>
+    </row>
+    <row r="48" spans="16:17">
+      <c r="P48"/>
+      <c r="Q48"/>
+    </row>
+    <row r="49" spans="16:17">
+      <c r="P49"/>
+      <c r="Q49"/>
+    </row>
+    <row r="50" spans="16:17">
+      <c r="P50"/>
+      <c r="Q50"/>
+    </row>
+    <row r="51" spans="16:17">
+      <c r="P51"/>
+      <c r="Q51"/>
+    </row>
+    <row r="52" spans="16:17">
+      <c r="P52"/>
+      <c r="Q52"/>
+    </row>
+    <row r="53" spans="16:17">
+      <c r="P53"/>
+      <c r="Q53"/>
+    </row>
+    <row r="54" spans="16:17">
+      <c r="P54"/>
+      <c r="Q54"/>
+    </row>
+    <row r="55" spans="16:17">
+      <c r="P55"/>
+      <c r="Q55"/>
+    </row>
+    <row r="56" spans="16:17">
+      <c r="P56"/>
+      <c r="Q56"/>
+    </row>
+    <row r="57" spans="16:17">
+      <c r="P57"/>
+      <c r="Q57"/>
+    </row>
+    <row r="58" spans="16:17">
+      <c r="P58"/>
+      <c r="Q58"/>
+    </row>
+    <row r="59" spans="16:17">
+      <c r="P59"/>
+      <c r="Q59"/>
+    </row>
+    <row r="60" spans="16:17">
+      <c r="P60"/>
+      <c r="Q60"/>
+    </row>
+    <row r="61" spans="16:17">
+      <c r="P61"/>
+      <c r="Q61"/>
+    </row>
+    <row r="62" spans="16:17">
+      <c r="P62"/>
+      <c r="Q62"/>
+    </row>
+    <row r="63" spans="16:17">
+      <c r="P63"/>
+      <c r="Q63"/>
+    </row>
+    <row r="64" spans="16:17">
+      <c r="P64"/>
+      <c r="Q64"/>
+    </row>
+    <row r="65" spans="16:17">
+      <c r="P65"/>
+      <c r="Q65"/>
+    </row>
+    <row r="66" spans="16:17">
+      <c r="P66"/>
+      <c r="Q66"/>
+    </row>
+    <row r="67" spans="16:17">
+      <c r="P67"/>
+      <c r="Q67"/>
+    </row>
+    <row r="68" spans="16:17">
+      <c r="P68"/>
+      <c r="Q68"/>
+    </row>
+    <row r="69" spans="16:17">
+      <c r="P69"/>
+      <c r="Q69"/>
+    </row>
+    <row r="70" spans="16:17">
+      <c r="P70"/>
+      <c r="Q70"/>
+    </row>
+    <row r="71" spans="16:17">
+      <c r="P71"/>
+      <c r="Q71"/>
+    </row>
+    <row r="72" spans="16:17">
+      <c r="P72"/>
+      <c r="Q72"/>
+    </row>
+    <row r="73" spans="16:17">
+      <c r="P73"/>
+      <c r="Q73"/>
+    </row>
+    <row r="74" spans="16:17">
+      <c r="P74"/>
+      <c r="Q74"/>
+    </row>
+    <row r="75" spans="16:17">
+      <c r="P75"/>
+      <c r="Q75"/>
+    </row>
+    <row r="76" spans="16:17">
+      <c r="P76"/>
+      <c r="Q76"/>
+    </row>
+    <row r="77" spans="16:17">
+      <c r="P77"/>
+      <c r="Q77"/>
+    </row>
+    <row r="78" spans="16:17">
+      <c r="P78"/>
+      <c r="Q78"/>
+    </row>
+    <row r="79" spans="16:17">
+      <c r="P79"/>
+      <c r="Q79"/>
+    </row>
+    <row r="80" spans="16:17">
+      <c r="P80"/>
+      <c r="Q80"/>
+    </row>
+    <row r="81" spans="16:17">
+      <c r="P81"/>
+      <c r="Q81"/>
+    </row>
+    <row r="82" spans="16:17">
+      <c r="P82"/>
+      <c r="Q82"/>
+    </row>
+    <row r="83" spans="16:17">
+      <c r="P83"/>
+      <c r="Q83"/>
+    </row>
+    <row r="84" spans="16:17">
+      <c r="P84"/>
+      <c r="Q84"/>
+    </row>
+    <row r="85" spans="16:17">
+      <c r="P85"/>
+      <c r="Q85"/>
+    </row>
+    <row r="86" spans="16:17">
+      <c r="P86"/>
+      <c r="Q86"/>
+    </row>
+    <row r="87" spans="16:17">
+      <c r="P87"/>
+      <c r="Q87"/>
+    </row>
+    <row r="88" spans="16:17">
+      <c r="P88"/>
+      <c r="Q88"/>
+    </row>
+    <row r="89" spans="16:17">
+      <c r="P89"/>
+      <c r="Q89"/>
+    </row>
+    <row r="90" spans="16:17">
+      <c r="P90"/>
+      <c r="Q90"/>
+    </row>
+    <row r="91" spans="16:17">
+      <c r="P91"/>
+      <c r="Q91"/>
+    </row>
+    <row r="92" spans="16:17">
+      <c r="P92"/>
+      <c r="Q92"/>
+    </row>
+    <row r="93" spans="16:17">
+      <c r="P93"/>
+      <c r="Q93"/>
+    </row>
+    <row r="94" spans="16:17">
+      <c r="P94"/>
+      <c r="Q94"/>
+    </row>
+    <row r="95" spans="16:17">
+      <c r="P95"/>
+      <c r="Q95"/>
+    </row>
+    <row r="96" spans="16:17">
+      <c r="P96"/>
+      <c r="Q96"/>
+    </row>
+    <row r="97" spans="16:17">
+      <c r="P97"/>
+      <c r="Q97"/>
+    </row>
+    <row r="98" spans="16:17">
+      <c r="P98"/>
+      <c r="Q98"/>
+    </row>
+    <row r="99" spans="16:17">
+      <c r="P99"/>
+      <c r="Q99"/>
+    </row>
+    <row r="100" spans="16:17">
+      <c r="P100"/>
+      <c r="Q100"/>
+    </row>
+    <row r="101" spans="16:17">
+      <c r="P101"/>
+      <c r="Q101"/>
+    </row>
+    <row r="102" spans="16:17">
+      <c r="P102"/>
+      <c r="Q102"/>
+    </row>
+    <row r="103" spans="16:17">
+      <c r="P103"/>
+      <c r="Q103"/>
+    </row>
+    <row r="104" spans="16:17">
+      <c r="P104"/>
+      <c r="Q104"/>
+    </row>
+    <row r="105" spans="16:17">
+      <c r="P105"/>
+      <c r="Q105"/>
+    </row>
+    <row r="106" spans="16:17">
+      <c r="P106"/>
+      <c r="Q106"/>
+    </row>
+    <row r="107" spans="16:17">
+      <c r="P107"/>
+      <c r="Q107"/>
+    </row>
+    <row r="108" spans="16:17">
+      <c r="P108"/>
+      <c r="Q108"/>
+    </row>
+    <row r="109" spans="16:17">
+      <c r="P109"/>
+      <c r="Q109"/>
+    </row>
+    <row r="110" spans="16:17">
+      <c r="P110"/>
+      <c r="Q110"/>
+    </row>
+    <row r="111" spans="16:17">
+      <c r="P111"/>
+      <c r="Q111"/>
+    </row>
+    <row r="112" spans="16:17">
+      <c r="P112"/>
+      <c r="Q112"/>
+    </row>
+    <row r="113" spans="16:17">
+      <c r="P113"/>
+      <c r="Q113"/>
+    </row>
+    <row r="114" spans="16:17">
+      <c r="P114"/>
+      <c r="Q114"/>
+    </row>
+    <row r="115" spans="16:17">
+      <c r="P115"/>
+      <c r="Q115"/>
+    </row>
+    <row r="116" spans="16:17">
+      <c r="P116"/>
+      <c r="Q116"/>
+    </row>
+    <row r="117" spans="16:17">
+      <c r="P117"/>
+      <c r="Q117"/>
+    </row>
+    <row r="118" spans="16:17">
+      <c r="P118"/>
+      <c r="Q118"/>
+    </row>
+    <row r="119" spans="16:17">
+      <c r="P119"/>
+      <c r="Q119"/>
+    </row>
+    <row r="120" spans="16:17">
+      <c r="P120"/>
+      <c r="Q120"/>
+    </row>
+    <row r="121" spans="16:17">
+      <c r="P121"/>
+      <c r="Q121"/>
+    </row>
+    <row r="122" spans="16:17">
+      <c r="P122"/>
+      <c r="Q122"/>
+    </row>
+    <row r="123" spans="16:17">
+      <c r="P123"/>
+      <c r="Q123"/>
+    </row>
+    <row r="124" spans="16:17">
+      <c r="P124"/>
+      <c r="Q124"/>
+    </row>
+    <row r="125" spans="16:17">
+      <c r="P125"/>
+      <c r="Q125"/>
+    </row>
+    <row r="126" spans="16:17">
+      <c r="P126"/>
+      <c r="Q126"/>
+    </row>
+    <row r="127" spans="16:17">
+      <c r="P127"/>
+      <c r="Q127"/>
+    </row>
+    <row r="128" spans="16:17">
+      <c r="P128"/>
+      <c r="Q128"/>
+    </row>
+    <row r="129" spans="16:17">
+      <c r="P129"/>
+      <c r="Q129"/>
+    </row>
+    <row r="130" spans="16:17">
+      <c r="P130"/>
+      <c r="Q130"/>
+    </row>
+    <row r="131" spans="16:17">
+      <c r="P131"/>
+      <c r="Q131"/>
+    </row>
+    <row r="132" spans="16:17">
+      <c r="P132"/>
+      <c r="Q132"/>
+    </row>
+    <row r="133" spans="16:17">
+      <c r="P133"/>
+      <c r="Q133"/>
+    </row>
+    <row r="134" spans="16:17">
+      <c r="P134"/>
+      <c r="Q134"/>
+    </row>
+    <row r="135" spans="16:17">
+      <c r="P135"/>
+      <c r="Q135"/>
+    </row>
+    <row r="136" spans="16:17">
+      <c r="P136"/>
+      <c r="Q136"/>
+    </row>
+    <row r="137" spans="16:17">
+      <c r="P137"/>
+      <c r="Q137"/>
+    </row>
+    <row r="138" spans="16:17">
+      <c r="P138"/>
+      <c r="Q138"/>
+    </row>
+    <row r="139" spans="16:17">
+      <c r="P139"/>
+      <c r="Q139"/>
+    </row>
+    <row r="140" spans="16:17">
+      <c r="P140"/>
+      <c r="Q140"/>
+    </row>
+    <row r="141" spans="16:17">
+      <c r="P141"/>
+      <c r="Q141"/>
+    </row>
+    <row r="142" spans="16:17">
+      <c r="P142"/>
+      <c r="Q142"/>
+    </row>
+    <row r="143" spans="16:17">
+      <c r="P143"/>
+      <c r="Q143"/>
+    </row>
+    <row r="144" spans="16:17">
+      <c r="P144"/>
+      <c r="Q144"/>
+    </row>
+    <row r="145" spans="16:17">
+      <c r="P145"/>
+      <c r="Q145"/>
+    </row>
+    <row r="146" spans="16:17">
+      <c r="P146"/>
+      <c r="Q146"/>
+    </row>
+    <row r="147" spans="16:17">
+      <c r="P147"/>
+      <c r="Q147"/>
+    </row>
+    <row r="148" spans="16:17">
+      <c r="P148"/>
+      <c r="Q148"/>
+    </row>
+    <row r="149" spans="16:17">
+      <c r="P149"/>
+      <c r="Q149"/>
+    </row>
+    <row r="150" spans="16:17">
+      <c r="P150"/>
+      <c r="Q150"/>
+    </row>
+    <row r="151" spans="16:17">
+      <c r="P151"/>
+      <c r="Q151"/>
+    </row>
+    <row r="152" spans="16:17">
+      <c r="P152"/>
+      <c r="Q152"/>
+    </row>
+    <row r="153" spans="16:17">
+      <c r="P153"/>
+      <c r="Q153"/>
+    </row>
+    <row r="154" spans="16:17">
+      <c r="P154"/>
+      <c r="Q154"/>
+    </row>
+    <row r="155" spans="16:17">
+      <c r="P155"/>
+      <c r="Q155"/>
+    </row>
+    <row r="156" spans="16:17">
+      <c r="P156"/>
+      <c r="Q156"/>
+    </row>
+    <row r="157" spans="16:17">
+      <c r="P157"/>
+      <c r="Q157"/>
+    </row>
+    <row r="158" spans="16:17">
+      <c r="P158"/>
+      <c r="Q158"/>
+    </row>
+    <row r="159" spans="16:17">
+      <c r="P159"/>
+      <c r="Q159"/>
+    </row>
+    <row r="160" spans="16:17">
+      <c r="P160"/>
+      <c r="Q160"/>
+    </row>
+    <row r="161" spans="16:17">
+      <c r="P161"/>
+      <c r="Q161"/>
+    </row>
+    <row r="162" spans="16:17">
+      <c r="P162"/>
+      <c r="Q162"/>
+    </row>
+    <row r="163" spans="16:17">
+      <c r="P163"/>
+      <c r="Q163"/>
+    </row>
+    <row r="164" spans="16:17">
+      <c r="P164"/>
+      <c r="Q164"/>
+    </row>
+    <row r="165" spans="16:17">
+      <c r="P165"/>
+      <c r="Q165"/>
+    </row>
+    <row r="166" spans="16:17">
+      <c r="P166"/>
+      <c r="Q166"/>
+    </row>
+    <row r="167" spans="16:17">
+      <c r="P167"/>
+      <c r="Q167"/>
+    </row>
+    <row r="168" spans="16:17">
+      <c r="P168"/>
+      <c r="Q168"/>
+    </row>
+    <row r="169" spans="16:17">
+      <c r="P169"/>
+      <c r="Q169"/>
+    </row>
+    <row r="170" spans="16:17">
+      <c r="P170"/>
+      <c r="Q170"/>
+    </row>
+    <row r="171" spans="16:17">
+      <c r="P171"/>
+      <c r="Q171"/>
+    </row>
+    <row r="172" spans="16:17">
+      <c r="P172"/>
+      <c r="Q172"/>
+    </row>
+    <row r="173" spans="16:17">
+      <c r="P173"/>
+      <c r="Q173"/>
+    </row>
+    <row r="174" spans="16:17">
+      <c r="P174"/>
+      <c r="Q174"/>
+    </row>
+    <row r="175" spans="16:17">
+      <c r="P175"/>
+      <c r="Q175"/>
+    </row>
+    <row r="176" spans="16:17">
+      <c r="P176"/>
+      <c r="Q176"/>
+    </row>
+    <row r="177" spans="16:17">
+      <c r="P177"/>
+      <c r="Q177"/>
+    </row>
+    <row r="178" spans="16:17">
+      <c r="P178"/>
+      <c r="Q178"/>
+    </row>
+    <row r="179" spans="16:17">
+      <c r="P179"/>
+      <c r="Q179"/>
+    </row>
+    <row r="180" spans="16:17">
+      <c r="P180"/>
+      <c r="Q180"/>
+    </row>
+    <row r="181" spans="16:17">
+      <c r="P181"/>
+      <c r="Q181"/>
+    </row>
+    <row r="182" spans="16:17">
+      <c r="P182"/>
+      <c r="Q182"/>
+    </row>
+    <row r="183" spans="16:17">
+      <c r="P183"/>
+      <c r="Q183"/>
+    </row>
+    <row r="184" spans="16:17">
+      <c r="P184"/>
+      <c r="Q184"/>
+    </row>
+    <row r="185" spans="16:17">
+      <c r="P185"/>
+      <c r="Q185"/>
+    </row>
+    <row r="186" spans="16:17">
+      <c r="P186"/>
+      <c r="Q186"/>
+    </row>
+    <row r="187" spans="16:17">
+      <c r="P187"/>
+      <c r="Q187"/>
+    </row>
+    <row r="188" spans="16:17">
+      <c r="P188"/>
+      <c r="Q188"/>
+    </row>
+    <row r="189" spans="16:17">
+      <c r="P189"/>
+      <c r="Q189"/>
+    </row>
+    <row r="190" spans="16:17">
+      <c r="P190"/>
+      <c r="Q190"/>
+    </row>
+    <row r="191" spans="16:17">
+      <c r="P191"/>
+      <c r="Q191"/>
+    </row>
+    <row r="192" spans="16:17">
+      <c r="P192"/>
+      <c r="Q192"/>
+    </row>
+    <row r="193" spans="16:17">
+      <c r="P193"/>
+      <c r="Q193"/>
+    </row>
+    <row r="194" spans="16:17">
+      <c r="P194"/>
+      <c r="Q194"/>
+    </row>
+    <row r="195" spans="16:17">
+      <c r="P195"/>
+      <c r="Q195"/>
+    </row>
+    <row r="196" spans="16:17">
+      <c r="P196"/>
+      <c r="Q196"/>
+    </row>
+    <row r="197" spans="16:17">
+      <c r="P197"/>
+      <c r="Q197"/>
+    </row>
+    <row r="198" spans="16:17">
+      <c r="P198"/>
+      <c r="Q198"/>
+    </row>
+    <row r="199" spans="16:17">
+      <c r="P199"/>
+      <c r="Q199"/>
     </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="H1:AA1"/>
-    <mergeCell ref="H2:AA2"/>
-    <mergeCell ref="H3:AA3"/>
-    <mergeCell ref="I4:L4"/>
-    <mergeCell ref="O4:W4"/>
-    <mergeCell ref="X4:Z4"/>
-    <mergeCell ref="I5:L5"/>
-    <mergeCell ref="O5:W5"/>
-    <mergeCell ref="X5:Z5"/>
-    <mergeCell ref="B10:B12"/>
-    <mergeCell ref="C10:C12"/>
-    <mergeCell ref="D10:D12"/>
-    <mergeCell ref="E10:E12"/>
-    <mergeCell ref="F10:F12"/>
-    <mergeCell ref="G10:G12"/>
-    <mergeCell ref="H10:H12"/>
-    <mergeCell ref="J10:J12"/>
-    <mergeCell ref="AA10:AA12"/>
+  <mergeCells count="9">
+    <mergeCell ref="H1:Y1"/>
+    <mergeCell ref="H2:Y2"/>
+    <mergeCell ref="H3:Y3"/>
+    <mergeCell ref="K4:N4"/>
+    <mergeCell ref="O4:P4"/>
+    <mergeCell ref="Q4:Y4"/>
+    <mergeCell ref="K5:N5"/>
+    <mergeCell ref="O5:P5"/>
+    <mergeCell ref="Q5:Y5"/>
   </mergeCells>
-  <dataValidations count="4">
-    <dataValidation type="custom" sqref="E1:E199 G1:H199">
+  <dataValidations count="5">
+    <dataValidation type="custom" sqref="E1:E199 G1:I199">
       <formula1>TRUE</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="I7:I1048576 L7:L1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="J7:J1048576">
+      <formula1>"小型,中型,大型,巨型"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="K7:K1048576">
       <formula1>"圆形,矩形"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="V7:V1048576 Y7:Y1048576">
+    <dataValidation type="list" sqref="O7:O1048576">
+      <formula1>"最大生命值,速度,开火间隔修正比例,发射间隔修正比例,子弹发射数"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="X7:X1048576">
       <formula1>"双侧,左侧,右侧"</formula1>
-    </dataValidation>
-    <dataValidation type="list" sqref="AA7:AA199 AD7:AD199">
-      <formula1>"true,false"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
